--- a/metrics/Global_Metrics_Ablation_Study_DT.xlsx
+++ b/metrics/Global_Metrics_Ablation_Study_DT.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,60 +471,180 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>MAE_constant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_constant</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_constant</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_constant</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2_constant</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_constant</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_constant</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_constant</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_stepwise</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_stepwise</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_stepwise</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_stepwise</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2_stepwise</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_stepwise</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_stepwise</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_stepwise</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>R2_dynamic</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_dynamic</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_dynamic</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_dynamic</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Int_Conf_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_RMSE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Pearson</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Spearman</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Kendall</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MAE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MedAE</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Max_Step</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Pred_Step</t>
         </is>
@@ -535,67 +655,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.322895680870901</v>
+        <v>2.246358961486059</v>
       </c>
       <c r="C2" t="n">
-        <v>2.513170131632456</v>
+        <v>2.176818573420292</v>
       </c>
       <c r="D2" t="n">
-        <v>7.267291778701691</v>
+        <v>6.56859873223117</v>
       </c>
       <c r="E2" t="n">
-        <v>2.695791493921904</v>
+        <v>2.562927765706863</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9088533421957548</v>
+        <v>0.926223368504667</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9537929879088981</v>
+        <v>0.9626815406516394</v>
       </c>
       <c r="H2" t="n">
-        <v>0.955724634870403</v>
+        <v>0.9630218240157419</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8226816582042795</v>
+        <v>0.8419919486686067</v>
       </c>
       <c r="J2" t="n">
-        <v>0.007753053933017506</v>
+        <v>2.891998753903604</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09717137116265295</v>
+        <v>2.955696483929119</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4770627839729827</v>
+        <v>9.498668164408942</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4783998530741153</v>
+        <v>3.081990941649398</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4063291653361568</v>
+        <v>0.8979522010260832</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1019362870771743</v>
+        <v>0.9629840823554341</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1451036926039053</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>0.9653620925295275</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.8614884548189454</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.270580801986726</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.358357307086803</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6.322847787818024</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.514527348791026</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.914644222232512</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9567597607355307</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.9525483034967164</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8201160096944388</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.99716785915201</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.876736093837846</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>5.649350905635503</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.376836322853448</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.9327557737727419</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.9703784575946967</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.9700095221715115</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.862346388870568</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.01471814818346912</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1621570633868317</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.008137289818381133</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.008178694419318955</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.0179001686401552</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.1583613953799639</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.2129833733800741</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="AQ2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AR2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AS2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -604,67 +796,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3497534287768402</v>
+        <v>0.3629134999967799</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2177297878538542</v>
+        <v>0.2224334886019397</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2595883361693449</v>
+        <v>0.2749409194996948</v>
       </c>
       <c r="E3" t="n">
-        <v>0.509498121850655</v>
+        <v>0.5243480900124409</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9537045115489587</v>
+        <v>0.9561343066074308</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9790902352473277</v>
+        <v>0.9795423334112117</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9831753676451819</v>
+        <v>0.9829740422877534</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8917554948851411</v>
+        <v>0.8919485689796214</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00739486661614086</v>
+        <v>0.2201181549735991</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0409490387255573</v>
+        <v>0.1959528066831825</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4901378147703739</v>
+        <v>0.0672301718943326</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4907605262116075</v>
+        <v>0.2592878167101814</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4431026369304717</v>
+        <v>0.9879400432432033</v>
       </c>
       <c r="O3" t="n">
-        <v>0.03065750976398782</v>
+        <v>0.9949047087639826</v>
       </c>
       <c r="P3" t="n">
-        <v>0.01802139193079663</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>0.9921748942063442</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9438011705562938</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.236129867876347</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1699424980429437</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.1218588972313726</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.3490829374681218</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.9587863798219869</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9864451452805254</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.987032435668558</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.9103206511566067</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.4902805801099296</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.348308044791505</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.4415622294001506</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6645014893889634</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9365358433912186</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.9788789130205935</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.9825771370504837</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.8927158855964186</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.00844811488827002</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.06109025403151452</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.004104418222657502</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.005019013451123155</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.015195233057821</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.03981331771950564</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.04767702943654857</v>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="AQ3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AR3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AS3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -673,67 +937,139 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.102430231533586</v>
+        <v>1.168412361993781</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6022992255642474</v>
+        <v>0.6409127015131777</v>
       </c>
       <c r="D4" t="n">
-        <v>2.938430452566704</v>
+        <v>3.305696089772122</v>
       </c>
       <c r="E4" t="n">
-        <v>1.714185069520413</v>
+        <v>1.818157333613382</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9535996906237701</v>
+        <v>0.95324080104971</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9765516029111448</v>
+        <v>0.9764696828652442</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9781097458336264</v>
+        <v>0.9746651714807083</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8801171970061014</v>
+        <v>0.8731614886340929</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007569725783813763</v>
+        <v>1.561036554140599</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1417173221960506</v>
+        <v>1.250060757078277</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4899854455135479</v>
+        <v>4.349097191141461</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4863528289349326</v>
+        <v>2.085448918372603</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4341103510865363</v>
+        <v>0.9483497843227451</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09425502889408133</v>
+        <v>0.9800776396901684</v>
       </c>
       <c r="P4" t="n">
-        <v>0.09116416845088171</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>0.9811378969547681</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.905141762950074</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.295796762483256</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.6346219354538951</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.498573232653492</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.120984024610627</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8897484208756393</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.9526555762371572</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.949347347465489</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.8328054018194526</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.9498409463764086</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.5352346769865512</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2.216466314997663</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.48878014327088</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9716167438127058</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9874808218365039</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.9835132472419846</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.8987744562996636</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.01193036875485881</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.2560212302617653</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.006066474351772599</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.007355190569752923</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01670135280527535</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.174793200075115</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.1142175555710072</v>
+      </c>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="AQ4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AR4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AS4" t="n">
         <v>1</v>
       </c>
     </row>
